--- a/Excel-Finance/Finance-And-Accounting-01/Data Validation.xlsx
+++ b/Excel-Finance/Finance-And-Accounting-01/Data Validation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\books-and-tutorials\Finance-Excel\Part 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Tests\j-l-data-science-data-analytics\Excel-Finance\Finance-And-Accounting-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521EB935-2514-41B2-9221-365129D25C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E4E011-6C6B-4259-81B4-EC2FEF9BCD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$19</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -703,15 +716,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -737,7 +750,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
@@ -763,7 +776,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>13</v>
       </c>
@@ -789,7 +802,7 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>17</v>
       </c>
@@ -815,7 +828,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>20</v>
       </c>
@@ -841,7 +854,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>23</v>
       </c>
@@ -867,7 +880,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>27</v>
       </c>
@@ -893,7 +906,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>31</v>
       </c>
@@ -919,7 +932,7 @@
         <v>48000</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>35</v>
       </c>
@@ -945,7 +958,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
@@ -971,7 +984,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>42</v>
       </c>
@@ -997,7 +1010,7 @@
         <v>38000</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>46</v>
       </c>
@@ -1023,7 +1036,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
@@ -1049,7 +1062,7 @@
         <v>98000</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>54</v>
       </c>
@@ -1075,7 +1088,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>57</v>
       </c>
@@ -1101,7 +1114,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>60</v>
       </c>
@@ -1127,7 +1140,7 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>63</v>
       </c>
@@ -1153,7 +1166,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>65</v>
       </c>
@@ -1179,7 +1192,7 @@
         <v>48000</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
         <v>36</v>
       </c>
@@ -1205,7 +1218,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1215,7 +1228,7 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1225,7 +1238,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1235,7 +1248,7 @@
       <c r="G22" s="1"/>
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1245,7 +1258,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1270,7 +1283,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0"/>
@@ -1280,7 +1293,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0"/>
